--- a/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -34,6 +34,18 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b</x:t>
+  </x:si>
+  <x:si>
     <x:t>Column1</x:t>
   </x:si>
   <x:si>
@@ -41,18 +53,6 @@
   </x:si>
   <x:si>
     <x:t>Column3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>b</x:t>
   </x:si>
   <x:si>
     <x:t>c</x:t>
@@ -594,93 +594,93 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="8"/>
       <x:c r="C9" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -708,27 +708,27 @@
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
@@ -760,27 +760,27 @@
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
@@ -808,82 +808,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="8"/>
       <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -905,27 +905,27 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
@@ -963,27 +963,27 @@
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
@@ -1011,82 +1011,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="5"/>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="8"/>
       <x:c r="C7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1108,82 +1108,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1205,82 +1205,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="7"/>
       <x:c r="B6" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B8" s="8"/>
       <x:c r="C8" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1302,27 +1302,27 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
@@ -1360,27 +1360,27 @@
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
@@ -1411,93 +1411,93 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="5"/>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="7"/>
       <x:c r="B5" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="8"/>
       <x:c r="C9" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1519,19 +1519,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="8"/>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="5"/>
     </x:row>
@@ -1557,58 +1557,58 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1847,81 +1847,81 @@
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="7"/>
       <x:c r="B1" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B8" s="8"/>
       <x:c r="C8" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -583,23 +583,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="3" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="3" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -684,19 +681,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -737,19 +727,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -790,19 +773,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -887,19 +863,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -940,19 +909,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -993,19 +955,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1090,19 +1045,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1187,19 +1135,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1284,19 +1225,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1337,19 +1271,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1390,33 +1317,26 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="3" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="3" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1501,19 +1421,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1536,23 +1449,16 @@
       <x:c r="C2" s="5"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
@@ -1616,19 +1522,12 @@
       <x:c r="B8" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1669,19 +1568,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1722,19 +1614,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1775,19 +1660,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1828,19 +1706,12 @@
       <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1925,10 +1796,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -1538,7 +1538,7 @@
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="10">
-        <x:v>1.05034722222222</x:v>
+        <x:v>1.0503472222222223</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
@@ -1625,32 +1625,32 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="13">
-        <x:v>0.00850694444444444</x:v>
+        <x:v>0.008506944444444444</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="14">
-        <x:v>0.0446180555555556</x:v>
+        <x:v>0.04461805555555556</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="9">
-        <x:v>0.0447916666666667</x:v>
+        <x:v>0.04479166666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="15">
-        <x:v>0.524548611111111</x:v>
+        <x:v>0.5245486111111111</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="10">
-        <x:v>1.05034722222222</x:v>
+        <x:v>1.0503472222222223</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="16">
-        <x:v>1.87586805555556</x:v>
+        <x:v>1.8758680555555556</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">

--- a/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -586,7 +586,7 @@
   <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="3" width="9.140625"/>
+    <x:col min="1" max="3" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1326,7 +1326,7 @@
   <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="3" width="9.140625"/>
+    <x:col min="1" max="3" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -1458,7 +1458,7 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="1" max="1" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
